--- a/artfynd/A 18199-2025 artfynd.xlsx
+++ b/artfynd/A 18199-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4215274</v>
+        <v>4168436</v>
       </c>
       <c r="B3" t="n">
-        <v>95518</v>
+        <v>95510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -906,6 +906,123 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4215274</v>
+      </c>
+      <c r="B4" t="n">
+        <v>95518</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ö-sidan av Flågefjäll, Smeviken, Boh</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>299162.7475960198</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6508478.601590668</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tanum</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Bohuslän</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Mo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>1999-10-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1999-10-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>granskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Föreningen Bohusläns Flora</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Föreningen Bohusläns Flora</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 18199-2025 artfynd.xlsx
+++ b/artfynd/A 18199-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4246051</v>
+        <v>4168436</v>
       </c>
       <c r="B2" t="n">
-        <v>95521</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,23 +686,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>221944</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -715,10 +706,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>299162.7475960198</v>
+        <v>299163</v>
       </c>
       <c r="R2" t="n">
-        <v>6508478.601590668</v>
+        <v>6508479</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -745,22 +736,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2000-05-20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-10-21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-05-20</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-10-21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4168436</v>
+        <v>4215274</v>
       </c>
       <c r="B3" t="n">
-        <v>95510</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +784,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221944</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +808,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>299162.7475960198</v>
+        <v>299163</v>
       </c>
       <c r="R3" t="n">
-        <v>6508478.601590668</v>
+        <v>6508479</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -865,19 +841,9 @@
           <t>1999-10-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1999-10-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +875,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>4215274</v>
+        <v>4246051</v>
       </c>
       <c r="B4" t="n">
-        <v>95518</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97986</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,16 +886,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>221946</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -949,10 +910,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>299162.7475960198</v>
+        <v>299163</v>
       </c>
       <c r="R4" t="n">
-        <v>6508478.601590668</v>
+        <v>6508479</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -979,22 +940,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1999-10-21</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-05-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1999-10-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-05-20</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 18199-2025 artfynd.xlsx
+++ b/artfynd/A 18199-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4168436</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4215274</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -974,8 +989,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4246051</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>